--- a/URBN.xlsx
+++ b/URBN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67299BC7-54B6-4EFB-83C0-9A82EF2675DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3970CDA8-4055-43BA-B0F7-41E8F94739AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{74F0CBED-AE29-49BC-826C-5A327DCF0A9C}"/>
   </bookViews>
@@ -680,7 +680,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="2">
-        <v>77.23</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -688,10 +688,10 @@
         <v>5</v>
       </c>
       <c r="J3" s="3">
-        <v>89.706922000000006</v>
+        <v>89.691297000000006</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -703,7 +703,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>6928.0655860600009</v>
+        <v>5874.7799535000004</v>
       </c>
       <c r="K4" s="4"/>
     </row>
@@ -715,11 +715,11 @@
         <v>7</v>
       </c>
       <c r="J5" s="3">
-        <f>306.6+305.133</f>
-        <v>611.73299999999995</v>
+        <f>369.206+326.724</f>
+        <v>695.93000000000006</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -730,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -739,7 +739,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>6316.3325860600007</v>
+        <v>5178.8499535000001</v>
       </c>
     </row>
   </sheetData>
@@ -826,9 +826,15 @@
       <c r="K3" s="6">
         <v>255</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
+      <c r="L3" s="6">
+        <v>257</v>
+      </c>
+      <c r="M3" s="6">
+        <v>258</v>
+      </c>
+      <c r="N3" s="6">
+        <v>253</v>
+      </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="7"/>
@@ -857,9 +863,15 @@
       <c r="K4" s="6">
         <v>239</v>
       </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
+      <c r="L4" s="6">
+        <v>243</v>
+      </c>
+      <c r="M4" s="6">
+        <v>248</v>
+      </c>
+      <c r="N4" s="6">
+        <v>254</v>
+      </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="7"/>
@@ -890,9 +902,15 @@
       <c r="K5" s="6">
         <v>230</v>
       </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
+      <c r="L5" s="6">
+        <v>247</v>
+      </c>
+      <c r="M5" s="6">
+        <v>253</v>
+      </c>
+      <c r="N5" s="6">
+        <v>268</v>
+      </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="7"/>
@@ -921,9 +939,15 @@
       <c r="K6" s="6">
         <v>9</v>
       </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
+      <c r="L6" s="6">
+        <v>9</v>
+      </c>
+      <c r="M6" s="6">
+        <v>9</v>
+      </c>
+      <c r="N6" s="6">
+        <v>9</v>
+      </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="7"/>
@@ -972,15 +996,15 @@
       </c>
       <c r="L7" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="M7" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="N7" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>784</v>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
@@ -1010,9 +1034,15 @@
       <c r="K8" s="6">
         <v>9</v>
       </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
+      <c r="L8" s="6">
+        <v>9</v>
+      </c>
+      <c r="M8" s="6">
+        <v>9</v>
+      </c>
+      <c r="N8" s="6">
+        <v>9</v>
+      </c>
       <c r="O8" s="6"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
@@ -1069,7 +1099,9 @@
       <c r="M10" s="7">
         <v>634.82799999999997</v>
       </c>
-      <c r="N10" s="7"/>
+      <c r="N10" s="7">
+        <v>774.89800000000002</v>
+      </c>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
@@ -1108,7 +1140,9 @@
       <c r="M11" s="7">
         <v>399.27199999999999</v>
       </c>
-      <c r="N11" s="7"/>
+      <c r="N11" s="7">
+        <v>451.02300000000002</v>
+      </c>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
@@ -1147,7 +1181,9 @@
       <c r="M12" s="7">
         <v>339.84800000000001</v>
       </c>
-      <c r="N12" s="7"/>
+      <c r="N12" s="7">
+        <v>405.10500000000002</v>
+      </c>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
@@ -1186,7 +1222,9 @@
       <c r="M13" s="7">
         <v>144.62899999999999</v>
       </c>
-      <c r="N13" s="7"/>
+      <c r="N13" s="7">
+        <v>160.50299999999999</v>
+      </c>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
@@ -1225,7 +1263,9 @@
       <c r="M14" s="7">
         <v>10.773</v>
       </c>
-      <c r="N14" s="7"/>
+      <c r="N14" s="7">
+        <v>10.241</v>
+      </c>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
@@ -1264,7 +1304,9 @@
       <c r="M15" s="7">
         <v>1296.454</v>
       </c>
-      <c r="N15" s="7"/>
+      <c r="N15" s="7">
+        <v>1566.443</v>
+      </c>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
@@ -1303,7 +1345,9 @@
       <c r="M16" s="7">
         <v>144.62899999999999</v>
       </c>
-      <c r="N16" s="7"/>
+      <c r="N16" s="7">
+        <v>160.50299999999999</v>
+      </c>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
@@ -1342,7 +1386,9 @@
       <c r="M17" s="7">
         <v>88.266999999999996</v>
       </c>
-      <c r="N17" s="7"/>
+      <c r="N17" s="7">
+        <v>74.823999999999998</v>
+      </c>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
@@ -1381,7 +1427,9 @@
       <c r="M18" s="9">
         <v>1529.35</v>
       </c>
-      <c r="N18" s="7"/>
+      <c r="N18" s="9">
+        <v>1801.77</v>
+      </c>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
@@ -1464,7 +1512,9 @@
         <f>964.034+1.989</f>
         <v>966.02300000000002</v>
       </c>
-      <c r="N19" s="7"/>
+      <c r="N19" s="7">
+        <v>1202.569</v>
+      </c>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
@@ -1545,7 +1595,7 @@
         <v>497.31900000000007</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" ref="J20:M20" si="3">+J18-J19</f>
+        <f t="shared" ref="J20:N20" si="3">+J18-J19</f>
         <v>527.68099999999981</v>
       </c>
       <c r="K20" s="3">
@@ -1560,7 +1610,10 @@
         <f t="shared" si="3"/>
         <v>563.32699999999988</v>
       </c>
-      <c r="N20" s="3"/>
+      <c r="N20" s="3">
+        <f t="shared" si="3"/>
+        <v>599.20100000000002</v>
+      </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
@@ -1640,7 +1693,9 @@
       <c r="M21" s="3">
         <v>419.00799999999998</v>
       </c>
-      <c r="N21" s="3"/>
+      <c r="N21" s="3">
+        <v>440.5</v>
+      </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
@@ -1721,7 +1776,7 @@
         <v>128.69100000000009</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" ref="J22:M22" si="5">+J20-J21</f>
+        <f t="shared" ref="J22:N22" si="5">+J20-J21</f>
         <v>125.31399999999979</v>
       </c>
       <c r="K22" s="3">
@@ -1736,7 +1791,10 @@
         <f t="shared" si="5"/>
         <v>144.3189999999999</v>
       </c>
-      <c r="N22" s="3"/>
+      <c r="N22" s="3">
+        <f t="shared" si="5"/>
+        <v>158.70100000000002</v>
+      </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
@@ -1815,7 +1873,9 @@
       <c r="M23" s="3">
         <v>8.1259999999999994</v>
       </c>
-      <c r="N23" s="3"/>
+      <c r="N23" s="3">
+        <v>-35.395000000000003</v>
+      </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
@@ -1896,7 +1956,7 @@
         <v>135.83200000000008</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" ref="J24:M24" si="7">+J22+J23</f>
+        <f t="shared" ref="J24:N24" si="7">+J22+J23</f>
         <v>130.90599999999981</v>
       </c>
       <c r="K24" s="3">
@@ -1911,7 +1971,10 @@
         <f t="shared" si="7"/>
         <v>152.44499999999991</v>
       </c>
-      <c r="N24" s="3"/>
+      <c r="N24" s="3">
+        <f t="shared" si="7"/>
+        <v>123.30600000000001</v>
+      </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
@@ -1990,7 +2053,9 @@
       <c r="M25" s="3">
         <v>36.003999999999998</v>
       </c>
-      <c r="N25" s="3"/>
+      <c r="N25" s="3">
+        <v>27.039000000000001</v>
+      </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
@@ -2071,7 +2136,7 @@
         <v>102.91100000000009</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" ref="J26:M26" si="9">+J24-J25</f>
+        <f t="shared" ref="J26:N26" si="9">+J24-J25</f>
         <v>120.3009999999998</v>
       </c>
       <c r="K26" s="3">
@@ -2086,7 +2151,10 @@
         <f t="shared" si="9"/>
         <v>116.44099999999992</v>
       </c>
-      <c r="N26" s="3"/>
+      <c r="N26" s="3">
+        <f t="shared" si="9"/>
+        <v>96.26700000000001</v>
+      </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
@@ -2242,7 +2310,10 @@
         <f>+M26/M29</f>
         <v>1.2980157763076512</v>
       </c>
-      <c r="N28" s="3"/>
+      <c r="N28" s="14">
+        <f>+N26/N29</f>
+        <v>1.0733148390082932</v>
+      </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
@@ -2321,7 +2392,9 @@
       <c r="M29" s="3">
         <v>89.706922000000006</v>
       </c>
-      <c r="N29" s="3"/>
+      <c r="N29" s="3">
+        <v>89.691297000000006</v>
+      </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
@@ -2463,7 +2536,7 @@
       </c>
       <c r="M31" s="15">
         <f t="shared" si="13"/>
-        <v>-1</v>
+        <v>5.0615595075239384E-2</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>

--- a/URBN.xlsx
+++ b/URBN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3970CDA8-4055-43BA-B0F7-41E8F94739AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1874CA08-9EFA-45E9-966C-8CED67D2E3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{74F0CBED-AE29-49BC-826C-5A327DCF0A9C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>URBN</t>
   </si>
@@ -208,6 +208,18 @@
   </si>
   <si>
     <t>Menus &amp; Venues Growth</t>
+  </si>
+  <si>
+    <t>Q127</t>
+  </si>
+  <si>
+    <t>Q227</t>
+  </si>
+  <si>
+    <t>Q327</t>
+  </si>
+  <si>
+    <t>Q427</t>
   </si>
 </sst>
 </file>
@@ -680,7 +692,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="2">
-        <v>65.5</v>
+        <v>74.28</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -688,10 +700,10 @@
         <v>5</v>
       </c>
       <c r="J3" s="3">
-        <v>89.691297000000006</v>
+        <v>87.503853000000007</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -703,7 +715,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>5874.7799535000004</v>
+        <v>6499.7862008400007</v>
       </c>
       <c r="K4" s="4"/>
     </row>
@@ -715,11 +727,11 @@
         <v>7</v>
       </c>
       <c r="J5" s="3">
-        <f>369.206+326.724</f>
-        <v>695.93000000000006</v>
+        <f>301.364+111.978</f>
+        <v>413.34199999999998</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -730,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -739,7 +751,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>5178.8499535000001</v>
+        <v>6086.444200840001</v>
       </c>
     </row>
   </sheetData>
@@ -802,6 +814,18 @@
       <c r="N2" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="O2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -835,7 +859,9 @@
       <c r="N3" s="6">
         <v>253</v>
       </c>
-      <c r="O3" s="6"/>
+      <c r="O3" s="6">
+        <v>252</v>
+      </c>
       <c r="P3" s="6"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -872,7 +898,9 @@
       <c r="N4" s="6">
         <v>254</v>
       </c>
-      <c r="O4" s="6"/>
+      <c r="O4" s="6">
+        <v>256</v>
+      </c>
       <c r="P4" s="6"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -911,7 +939,9 @@
       <c r="N5" s="6">
         <v>268</v>
       </c>
-      <c r="O5" s="6"/>
+      <c r="O5" s="6">
+        <v>276</v>
+      </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -948,7 +978,9 @@
       <c r="N6" s="6">
         <v>9</v>
       </c>
-      <c r="O6" s="6"/>
+      <c r="O6" s="6">
+        <v>8</v>
+      </c>
       <c r="P6" s="6"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
@@ -987,7 +1019,7 @@
         <v>731</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" ref="J7:N7" si="1">+SUM(J3:J6)</f>
+        <f t="shared" ref="J7:O7" si="1">+SUM(J3:J6)</f>
         <v>733</v>
       </c>
       <c r="K7" s="8">
@@ -1006,7 +1038,10 @@
         <f t="shared" si="1"/>
         <v>784</v>
       </c>
-      <c r="O7" s="9"/>
+      <c r="O7" s="8">
+        <f t="shared" si="1"/>
+        <v>792</v>
+      </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
@@ -1043,7 +1078,9 @@
       <c r="N8" s="6">
         <v>9</v>
       </c>
-      <c r="O8" s="6"/>
+      <c r="O8" s="6">
+        <v>9</v>
+      </c>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -1102,7 +1139,9 @@
       <c r="N10" s="7">
         <v>774.89800000000002</v>
       </c>
-      <c r="O10" s="7"/>
+      <c r="O10" s="7">
+        <v>589.07299999999998</v>
+      </c>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -1143,7 +1182,9 @@
       <c r="N11" s="7">
         <v>451.02300000000002</v>
       </c>
-      <c r="O11" s="7"/>
+      <c r="O11" s="7">
+        <v>411.71899999999999</v>
+      </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -1184,7 +1225,9 @@
       <c r="N12" s="7">
         <v>405.10500000000002</v>
       </c>
-      <c r="O12" s="7"/>
+      <c r="O12" s="7">
+        <v>304.72699999999998</v>
+      </c>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
@@ -1225,7 +1268,9 @@
       <c r="N13" s="7">
         <v>160.50299999999999</v>
       </c>
-      <c r="O13" s="7"/>
+      <c r="O13" s="7">
+        <v>167.26400000000001</v>
+      </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -1266,7 +1311,9 @@
       <c r="N14" s="7">
         <v>10.241</v>
       </c>
-      <c r="O14" s="7"/>
+      <c r="O14" s="7">
+        <v>8.5619999999999994</v>
+      </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -1307,7 +1354,9 @@
       <c r="N15" s="7">
         <v>1566.443</v>
       </c>
-      <c r="O15" s="7"/>
+      <c r="O15" s="7">
+        <v>1220.914</v>
+      </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -1348,7 +1397,9 @@
       <c r="N16" s="7">
         <v>160.50299999999999</v>
       </c>
-      <c r="O16" s="7"/>
+      <c r="O16" s="7">
+        <v>167.26400000000001</v>
+      </c>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -1389,7 +1440,9 @@
       <c r="N17" s="7">
         <v>74.823999999999998</v>
       </c>
-      <c r="O17" s="7"/>
+      <c r="O17" s="7">
+        <v>93.167000000000002</v>
+      </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
@@ -1430,7 +1483,9 @@
       <c r="N18" s="9">
         <v>1801.77</v>
       </c>
-      <c r="O18" s="7"/>
+      <c r="O18" s="9">
+        <v>1481.345</v>
+      </c>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
@@ -1515,7 +1570,9 @@
       <c r="N19" s="7">
         <v>1202.569</v>
       </c>
-      <c r="O19" s="7"/>
+      <c r="O19" s="7">
+        <v>938.779</v>
+      </c>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
@@ -1595,7 +1652,7 @@
         <v>497.31900000000007</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" ref="J20:N20" si="3">+J18-J19</f>
+        <f t="shared" ref="J20:O20" si="3">+J18-J19</f>
         <v>527.68099999999981</v>
       </c>
       <c r="K20" s="3">
@@ -1614,7 +1671,10 @@
         <f t="shared" si="3"/>
         <v>599.20100000000002</v>
       </c>
-      <c r="O20" s="3"/>
+      <c r="O20" s="3">
+        <f t="shared" si="3"/>
+        <v>542.56600000000003</v>
+      </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
@@ -1696,7 +1756,9 @@
       <c r="N21" s="3">
         <v>440.5</v>
       </c>
-      <c r="O21" s="3"/>
+      <c r="O21" s="3">
+        <v>402.88499999999999</v>
+      </c>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
@@ -1776,7 +1838,7 @@
         <v>128.69100000000009</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" ref="J22:N22" si="5">+J20-J21</f>
+        <f t="shared" ref="J22:O22" si="5">+J20-J21</f>
         <v>125.31399999999979</v>
       </c>
       <c r="K22" s="3">
@@ -1795,7 +1857,10 @@
         <f t="shared" si="5"/>
         <v>158.70100000000002</v>
       </c>
-      <c r="O22" s="3"/>
+      <c r="O22" s="3">
+        <f t="shared" si="5"/>
+        <v>139.68100000000004</v>
+      </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
@@ -1876,7 +1941,9 @@
       <c r="N23" s="3">
         <v>-35.395000000000003</v>
       </c>
-      <c r="O23" s="3"/>
+      <c r="O23" s="3">
+        <v>6.1849999999999996</v>
+      </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
@@ -1956,7 +2023,7 @@
         <v>135.83200000000008</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" ref="J24:N24" si="7">+J22+J23</f>
+        <f t="shared" ref="J24:O24" si="7">+J22+J23</f>
         <v>130.90599999999981</v>
       </c>
       <c r="K24" s="3">
@@ -1975,7 +2042,10 @@
         <f t="shared" si="7"/>
         <v>123.30600000000001</v>
       </c>
-      <c r="O24" s="3"/>
+      <c r="O24" s="3">
+        <f t="shared" si="7"/>
+        <v>145.86600000000004</v>
+      </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
@@ -2056,7 +2126,9 @@
       <c r="N25" s="3">
         <v>27.039000000000001</v>
       </c>
-      <c r="O25" s="3"/>
+      <c r="O25" s="3">
+        <v>30.161000000000001</v>
+      </c>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
@@ -2136,7 +2208,7 @@
         <v>102.91100000000009</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" ref="J26:N26" si="9">+J24-J25</f>
+        <f t="shared" ref="J26:O26" si="9">+J24-J25</f>
         <v>120.3009999999998</v>
       </c>
       <c r="K26" s="3">
@@ -2155,7 +2227,10 @@
         <f t="shared" si="9"/>
         <v>96.26700000000001</v>
       </c>
-      <c r="O26" s="3"/>
+      <c r="O26" s="3">
+        <f t="shared" si="9"/>
+        <v>115.70500000000004</v>
+      </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
@@ -2314,7 +2389,10 @@
         <f>+N26/N29</f>
         <v>1.0733148390082932</v>
       </c>
-      <c r="O28" s="3"/>
+      <c r="O28" s="14">
+        <f>+O26/O29</f>
+        <v>1.3222846312836081</v>
+      </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
@@ -2395,7 +2473,9 @@
       <c r="N29" s="3">
         <v>89.691297000000006</v>
       </c>
-      <c r="O29" s="3"/>
+      <c r="O29" s="3">
+        <v>87.503853000000007</v>
+      </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
@@ -2538,8 +2618,14 @@
         <f t="shared" si="13"/>
         <v>5.0615595075239384E-2</v>
       </c>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
+      <c r="N31" s="15">
+        <f t="shared" ref="N31" si="14">+N7/J7-1</f>
+        <v>6.9577080491132426E-2</v>
+      </c>
+      <c r="O31" s="15">
+        <f t="shared" ref="O31" si="15">+O7/K7-1</f>
+        <v>8.0491132332878523E-2</v>
+      </c>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
@@ -2595,19 +2681,19 @@
       <c r="E32" s="15"/>
       <c r="F32" s="15"/>
       <c r="G32" s="15" t="e">
-        <f t="shared" ref="G32:J36" si="14">+G10/C10-1</f>
+        <f t="shared" ref="G32:J36" si="16">+G10/C10-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H32" s="15" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I32" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>6.930280692373314E-2</v>
       </c>
       <c r="J32" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>9.345659608784973E-2</v>
       </c>
       <c r="K32" s="15">
@@ -2622,8 +2708,14 @@
         <f>+M10/I10-1</f>
         <v>7.9780855656267802E-2</v>
       </c>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
+      <c r="N32" s="15">
+        <f t="shared" ref="N32:O36" si="17">+N10/J10-1</f>
+        <v>4.2889250770493881E-2</v>
+      </c>
+      <c r="O32" s="15">
+        <f t="shared" si="17"/>
+        <v>3.3586521877209563E-2</v>
+      </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
@@ -2679,35 +2771,41 @@
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
       <c r="G33" s="15" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H33" s="15" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I33" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.10273621643779474</v>
       </c>
       <c r="J33" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-0.14256927230267269</v>
       </c>
       <c r="K33" s="15">
-        <f t="shared" ref="K33:M36" si="15">+K11/G11-1</f>
+        <f t="shared" ref="K33:M36" si="18">+K11/G11-1</f>
         <v>0.10800744294630249</v>
       </c>
       <c r="L33" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.1366229469584721</v>
       </c>
       <c r="M33" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>9.1333499154040876E-2</v>
       </c>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
+      <c r="N33" s="15">
+        <f t="shared" si="17"/>
+        <v>0.45201823461615231</v>
+      </c>
+      <c r="O33" s="15">
+        <f t="shared" si="17"/>
+        <v>0.16597283581413258</v>
+      </c>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
@@ -2763,35 +2861,41 @@
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
       <c r="G34" s="15" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H34" s="15" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I34" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-7.3365703275529826E-2</v>
       </c>
       <c r="J34" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-3.3212907243280299E-2</v>
       </c>
       <c r="K34" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>1.2014445455823752E-2</v>
       </c>
       <c r="L34" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>5.1958385299085919E-2</v>
       </c>
       <c r="M34" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.13065204589838886</v>
       </c>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
+      <c r="N34" s="15">
+        <f t="shared" si="17"/>
+        <v>0.12469183102345416</v>
+      </c>
+      <c r="O34" s="15">
+        <f t="shared" si="17"/>
+        <v>0.11415513427542456</v>
+      </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
@@ -2847,35 +2951,41 @@
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
       <c r="G35" s="15" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H35" s="15" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I35" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.48409548812503811</v>
       </c>
       <c r="J35" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.94235890932149657</v>
       </c>
       <c r="K35" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.59546842523928056</v>
       </c>
       <c r="L35" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.53184263914615859</v>
       </c>
       <c r="M35" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.48746297515221326</v>
       </c>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
+      <c r="N35" s="15">
+        <f t="shared" si="17"/>
+        <v>0.30997192386797678</v>
+      </c>
+      <c r="O35" s="15">
+        <f t="shared" si="17"/>
+        <v>0.34506328706756517</v>
+      </c>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
@@ -2931,35 +3041,41 @@
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
       <c r="G36" s="15" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H36" s="15" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I36" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>5.9224102352455565E-2</v>
       </c>
       <c r="J36" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.11395295729618637</v>
       </c>
       <c r="K36" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.15329935622317592</v>
       </c>
       <c r="L36" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>3.5371644539199387E-2</v>
       </c>
       <c r="M36" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>4.9386323787258934E-2</v>
       </c>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
+      <c r="N36" s="15">
+        <f t="shared" si="17"/>
+        <v>4.9712997129971237E-2</v>
+      </c>
+      <c r="O36" s="15">
+        <f t="shared" si="17"/>
+        <v>-4.3028259099896493E-3</v>
+      </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
@@ -3015,35 +3131,41 @@
       <c r="E37" s="16"/>
       <c r="F37" s="16"/>
       <c r="G37" s="17" t="e">
-        <f t="shared" ref="G37:M37" si="16">+G18/C18-1</f>
+        <f t="shared" ref="G37:M37" si="19">+G18/C18-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H37" s="17" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I37" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>6.2974272034868051E-2</v>
       </c>
       <c r="J37" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.10087915844095718</v>
       </c>
       <c r="K37" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.10724208232977883</v>
       </c>
       <c r="L37" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.11301822022709263</v>
       </c>
       <c r="M37" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.12299033303839235</v>
       </c>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
+      <c r="N37" s="17">
+        <f t="shared" ref="N37" si="20">+N18/J18-1</f>
+        <v>0.10124562990489694</v>
+      </c>
+      <c r="O37" s="17">
+        <f t="shared" ref="O37" si="21">+O18/K18-1</f>
+        <v>0.1142112717478212</v>
+      </c>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
@@ -3095,27 +3217,27 @@
         <v>29</v>
       </c>
       <c r="C38" s="15" t="e">
-        <f t="shared" ref="C38:H38" si="17">+C20/C18</f>
+        <f t="shared" ref="C38:H38" si="22">+C20/C18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D38" s="15" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E38" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0.35468016054025442</v>
       </c>
       <c r="F38" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0.29214557453468387</v>
       </c>
       <c r="G38" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>0.34011336418118282</v>
       </c>
       <c r="H38" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="I38" s="15">
@@ -3138,8 +3260,14 @@
         <f>+M20/M18</f>
         <v>0.36834406774119721</v>
       </c>
-      <c r="N38" s="3"/>
-      <c r="O38" s="3"/>
+      <c r="N38" s="15">
+        <f t="shared" ref="N38:O38" si="23">+N20/N18</f>
+        <v>0.33256242472679642</v>
+      </c>
+      <c r="O38" s="15">
+        <f t="shared" si="23"/>
+        <v>0.36626579223610978</v>
+      </c>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
@@ -3191,27 +3319,27 @@
         <v>30</v>
       </c>
       <c r="C39" s="15" t="e">
-        <f t="shared" ref="C39:H39" si="18">+C22/C18</f>
+        <f t="shared" ref="C39:H39" si="24">+C22/C18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D39" s="15" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E39" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>8.5061045572264155E-2</v>
       </c>
       <c r="F39" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>3.8579081869527097E-2</v>
       </c>
       <c r="G39" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>6.2148755925552052E-2</v>
       </c>
       <c r="H39" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="I39" s="15">
@@ -3234,8 +3362,14 @@
         <f>+M22/M18</f>
         <v>9.4366234020989245E-2</v>
       </c>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
+      <c r="N39" s="15">
+        <f t="shared" ref="N39:O39" si="25">+N22/N18</f>
+        <v>8.8080609622759848E-2</v>
+      </c>
+      <c r="O39" s="15">
+        <f t="shared" si="25"/>
+        <v>9.4293361775953641E-2</v>
+      </c>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
@@ -3287,27 +3421,27 @@
         <v>31</v>
       </c>
       <c r="C40" s="15" t="e">
-        <f t="shared" ref="C40:H40" si="19">+C25/C24</f>
+        <f t="shared" ref="C40:H40" si="26">+C25/C24</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D40" s="15" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E40" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0.24314615756315941</v>
       </c>
       <c r="F40" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0.25418196017180811</v>
       </c>
       <c r="G40" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0.23624335353035747</v>
       </c>
       <c r="H40" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="I40" s="15">
@@ -3330,8 +3464,14 @@
         <f>+M25/M24</f>
         <v>0.23617698186231112</v>
       </c>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
+      <c r="N40" s="15">
+        <f t="shared" ref="N40:O40" si="27">+N25/N24</f>
+        <v>0.21928373315167143</v>
+      </c>
+      <c r="O40" s="15">
+        <f t="shared" si="27"/>
+        <v>0.20677196879327597</v>
+      </c>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
